--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260714.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>172,341,000</t>
+          <t>175,241,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.71%</t>
+          <t>11.07%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.07%</t>
+          <t>9.95%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>372,689,486</t>
+          <t>370,889,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>5.92%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>184,896,000</t>
+          <t>184,490,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.63%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>38,437,000</t>
+          <t>38,327,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.48%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>111,174,000</t>
+          <t>110,574,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>571,227,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,975,000</t>
+          <t>4,955,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>28,330,000</t>
+          <t>28,250,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>96,642,442</t>
+          <t>96,142,442</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>25,744,000</t>
+          <t>131,319,945</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>132,519,945</t>
+          <t>25,544,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>373,225,000</t>
+          <t>373,725,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -1051,56 +1051,56 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>149,152,000</t>
+          <t>148,152,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>61,890,000</t>
+          <t>101,917,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>101,917,000</t>
+          <t>61,690,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>184,756,000</t>
+          <t>188,806,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>81,868,000</t>
+          <t>81,418,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>278,866,000</t>
+          <t>276,366,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,583,000</t>
+          <t>14,433,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,574,461,363</t>
+          <t>14,443,141,473</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,214,593,385</t>
+          <t>2,913,439,785</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
